--- a/source/Part_02_Excel/M1/tasks/pre_0/a/PCA01_PowerData_login.xlsx
+++ b/source/Part_02_Excel/M1/tasks/pre_0/a/PCA01_PowerData_login.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewil\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9270CB6C-B43F-4BF3-902D-22C664D55230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD51D233-DE4B-466D-89F0-90919950C5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{DEDA1C8B-1553-4801-B352-B17DEFC5138D}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DEDA1C8B-1553-4801-B352-B17DEFC5138D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -113,16 +113,16 @@
     <t>Energy Conversion</t>
   </si>
   <si>
-    <t>Energy (kWh)</t>
-  </si>
-  <si>
-    <t>Energy (J)</t>
-  </si>
-  <si>
     <t>Performance Adjustment Factor</t>
   </si>
   <si>
-    <t>Adjusted Energy (kWh)</t>
+    <t>Energy Usage (kWh)</t>
+  </si>
+  <si>
+    <t>Adjusted Energy Usage (kWh)</t>
+  </si>
+  <si>
+    <t>Energy Usage (J)</t>
   </si>
 </sst>
 </file>
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,7 +334,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -365,40 +364,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -453,13 +418,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -472,6 +430,47 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -488,10 +487,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A2B6826-DC59-4750-922B-68A3BFDBA1BB}" name="Table1" displayName="Table1" ref="E6:F13" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A2B6826-DC59-4750-922B-68A3BFDBA1BB}" name="Table1" displayName="Table1" ref="E6:F13" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D4A9AFA8-4B39-4201-A9CE-DB6B0C5ADA58}" name="header" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{DC320AFE-0C9C-46C6-BA36-7056BA730529}" name="header2" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D4A9AFA8-4B39-4201-A9CE-DB6B0C5ADA58}" name="header" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{DC320AFE-0C9C-46C6-BA36-7056BA730529}" name="header2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -820,7 +819,8 @@
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
     <col min="2" max="4" width="8.84375" style="2"/>
     <col min="5" max="5" width="19.53515625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="14.3046875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.3046875" style="2" customWidth="1"/>
     <col min="8" max="8" width="27.15234375" style="2" customWidth="1"/>
     <col min="9" max="16384" width="8.84375" style="2"/>
   </cols>
@@ -856,72 +856,72 @@
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>27</v>
+      <c r="H6" s="25" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <v>120</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="26">
         <v>1.08</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="2">
         <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="2">
         <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="2">
         <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="2">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="2">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="2">
         <v>112</v>
       </c>
     </row>
@@ -966,95 +966,95 @@
       </c>
     </row>
     <row r="23" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="25" t="s">
+      <c r="F23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="25" t="s">
+      <c r="G23" s="24" t="s">
         <v>28</v>
       </c>
+      <c r="H23" s="24" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="8">
         <f>F7</f>
         <v>120</v>
       </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
     </row>
     <row r="25" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="9">
         <f t="shared" ref="F25:F30" si="0">F8</f>
         <v>135</v>
       </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
     </row>
     <row r="26" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="13" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="9">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
     </row>
     <row r="27" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="13" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="9">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
     </row>
     <row r="28" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="9">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
     </row>
     <row r="29" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
     </row>
     <row r="30" spans="5:8" x14ac:dyDescent="0.4">
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="10">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
